--- a/processed_ruby_restored_xlsx/sc141_みるく１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc141_みるく１：風呂.ss.xlsx
@@ -605,8 +605,8 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Feeling somewhat better, I gave a vigorous nod and got
-out of the tub.</t>
+          <t>Feeling somewhat better, I gave a vigorous nod and
+got out of the tub.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -713,8 +713,8 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>But doing something pointless all by yourself, with no
-one watching, is kind of fun.</t>
+          <t>But doing something pointless all by yourself, with
+no one watching, is kind of fun.</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1278,7 +1278,8 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan's voice and movements are softer than usual.</t>
+          <t>Miru-chan's voice and movements are softer than
+usual.</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2489,8 +2490,8 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Ah, looking at her again, she's so small she could fit
-snugly in my arms...</t>
+          <t>Ah, looking at her again, she's so small she could
+fit snugly in my arms...</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3327,8 +3328,8 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>The words slipped out before I could stop them, making
-Miru-chan shrink even tighter.</t>
+          <t>The words slipped out before I could stop them,
+making Miru-chan shrink even tighter.</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3435,9 +3436,9 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>I ruffled her hair a little, patting it roughly enough
-to mess it up, and Miru-chan's shoulders trembled a
-bit.</t>
+          <t>I ruffled her hair a little, patting it roughly
+enough to mess it up, and Miru-chan's shoulders
+trembled a bit.</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3608,8 +3609,8 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>I'll just keep patting her head like this and wash her
-hair for her.</t>
+          <t>I'll just keep patting her head like this and wash
+her hair for her.</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -4178,8 +4179,8 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>A thin line of pale pink—the secret place of Miru-chan
-who still doesn't know anything...</t>
+          <t>A thin line of pale pink—the secret place of
+Miru-chan who still doesn't know anything...</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4347,8 +4348,8 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>I, driven by a rising impulse, kissed Miru-chan's down
-there.</t>
+          <t>I, driven by a rising impulse, kissed Miru-chan's
+down there.</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4393,8 +4394,8 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>Even though I only touched her for a moment, Miru-chan
-writhed and twisted her body in agony.</t>
+          <t>Even though I only touched her for a moment,
+Miru-chan writhed and twisted her body in agony.</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4470,7 +4471,8 @@
       <c r="B262" s="1" t="inlineStr">
         <is>
           <t>Even though I only touched her and hadn’t done
-anything else, Miru-chan let out a high-pitched sound.</t>
+anything else, Miru-chan let out a high-pitched
+sound.</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4561,8 +4563,8 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>Soft thighs are pressing my cheek in and in, making me
-get more and more turned on.</t>
+          <t>Soft thighs are pressing my cheek in and in, making
+me get more and more turned on.</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4669,7 +4671,8 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>「Hey, I'm trying to wash it, you know？ Hehe... smooch」</t>
+          <t>「Hey, I'm trying to wash it, you know？ Hehe...
+smooch」</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4789,8 +4792,8 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ah, aaah！ Onii-chan, onii—n—！ It tickl—...es...
-I might...」</t>
+          <t>「Ah... ah, aaah！ Onii-chan, onii—n—！ It
+tickl—...es... I might...」</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4897,8 +4900,8 @@
       <c r="B290" s="1" t="inlineStr">
         <is>
           <t>I press my tongue against that spot that probably
-doesn't even know what it means to be wet yet, soaking
-it thoroughly with my saliva.</t>
+doesn't even know what it means to be wet yet,
+soaking it thoroughly with my saliva.</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -5160,7 +5163,8 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>「Perrr, lero… *chu！* Miru-chan… does this feel good…？」</t>
+          <t>「Perrr, lero… *chu！* Miru-chan… does this feel
+good…？」</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5222,8 +5226,8 @@
       <c r="B311" s="1" t="inlineStr">
         <is>
           <t>Maybe because I put it into words and paid attention
-to it, that strange, odd feeling might be turning into
-something pleasant.</t>
+to it, that strange, odd feeling might be turning
+into something pleasant.</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5314,7 +5318,8 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it, I do get called pervy a lot, huh.</t>
+          <t>Come to think of it, I do get called pervy a lot,
+huh.</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5595,8 +5600,8 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>Press my mouth hard against Miru-chan's there and suck
-with all my might.</t>
+          <t>Press my mouth hard against Miru-chan's there and
+suck with all my might.</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5611,8 +5616,8 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>Just as you’re about to pull your hips back, grab hold
-of them tight...</t>
+          <t>Just as you’re about to pull your hips back, grab
+hold of them tight...</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5886,8 +5891,8 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>What fills my mouth is Miru-chan’s love juices... just
-a little, but I can almost taste a sweetness.</t>
+          <t>What fills my mouth is Miru-chan’s love juices...
+just a little, but I can almost taste a sweetness.</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6115,8 +6120,8 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan repeats it like a mantra, letting her tongue
-dangle slackly to show it.</t>
+          <t>Miru-chan repeats it like a mantra, letting her
+tongue dangle slackly to show it.</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -6223,8 +6228,8 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>After sucking once… the tongue drags wetly along, then
-carries it back into her mouth.</t>
+          <t>After sucking once… the tongue drags wetly along,
+then carries it back into her mouth.</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6502,8 +6507,8 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>I press my tongue firmly against it and loosen it more
-and more.</t>
+          <t>I press my tongue firmly against it and loosen it
+more and more.</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -6658,8 +6663,8 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>Each time it's repeated, Miru-chan's body becomes more
-responsive.</t>
+          <t>Each time it's repeated, Miru-chan's body becomes
+more responsive.</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -7644,8 +7649,8 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>She looks up at me in a troubled way, tears welling in
-her eyes.</t>
+          <t>She looks up at me in a troubled way, tears welling
+in her eyes.</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -8430,8 +8435,8 @@
       </c>
       <c r="B519" s="1" t="inlineStr">
         <is>
-          <t>The taste... is kind of between orange juice and lemon
-juice, I guess.</t>
+          <t>The taste... is kind of between orange juice and
+lemon juice, I guess.</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -8766,7 +8771,8 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>I got carried away and ended up making Miru-chan sulk.</t>
+          <t>I got carried away and ended up making Miru-chan
+sulk.</t>
         </is>
       </c>
       <c r="C541" t="n">

--- a/processed_ruby_restored_xlsx/sc141_みるく１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc141_みるく１：風呂.ss.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Then at the washing area, I filled a bucket to the
+          <t>Then at the washing area, he filled a bucket to the
 brim with hot water.</t>
         </is>
       </c>
@@ -637,8 +637,8 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>And from there... I douse myself from the head with
-all my might！</t>
+          <t>And from there... he douses himself from the head
+with all his might！</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>「Uuuuuuu—！！」</t>
+          <t>Uuuuuuu—！！</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>「Yeah！ I guess so... huh？」</t>
+          <t>Yeah！ I guess so... huh？</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah...！」</t>
+          <t>Y-yeah...！</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>My penis kept swelling bigger and bigger...</t>
+          <t>Her penis kept swelling bigger and bigger...</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3808,8 +3808,8 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>Until now, I must have felt safe thinking no one was
-watching because I was standing behind me.</t>
+          <t>Until now, he must have felt safe thinking no one was
+watching because I was standing behind him.</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnh...！」</t>
+          <t>Nn... nnh...！</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3901,8 +3901,8 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>Even though it's not the first time she's exposed
-herself naked in front of me, that doesn't mean she's
+          <t>Even though it's not the first time I've exposed
+myself naked in front of them, that doesn't mean I'm
 okay with it.</t>
         </is>
       </c>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>「W-w... wha—what！？」</t>
+          <t>W-w... wha—what！？</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>「Ughhh… Onii-chan, you perv！」</t>
+          <t>Ughhh… Onii-chan, you perv！</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4547,8 +4547,8 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>She clamps my face between her hands... like she's
-deliberately making sure I can't get away...</t>
+          <t>They clamp my face between their hands... like
+they're deliberately making sure I can't get away...</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>「Nngh！ Hey, Miru-chan... it hurts, it hurts」</t>
+          <t>Nngh！ Hey, Miru-chan... it hurts, it hurts</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>「Mwah… What's so weird about it, hmm？」</t>
+          <t>Mwah… What's so weird about it, hmm？</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t>「Waaahhhh… uh, uffu！ n'aa…！ fuu, fuuuuu…'…」</t>
+          <t>Waaahhhh… uh, uffu！ n'aa…！ fuu, fuuuuu…」…</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>「chu, chu... pero, peropero...」</t>
+          <t>chu, chu... pero, peropero...</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh！ Is it... overflowing？ Wha, what is it？ Nn！」</t>
+          <t>Aahhh！ Is it... overflowing？ Wha, what is it？ Nn！</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>「Nmm, n...chu...kk, gulp...」</t>
+          <t>Nmm, n...chu...kk, gulp...</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -6647,8 +6647,8 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>「Fah, ah！ Hah！ Aahhh... it fe-els... so good...
-fe-els... so... good...」</t>
+          <t>Fah, ah！ Hah！ Aahhh... it fe-els... so good...
+fe-els... so... good...</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6772,8 +6772,8 @@
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t>It really feels good, but since it’s my first time I
-should still be gentle with me…</t>
+          <t>It really feels good, but since it’s his first time I
+should still be gentle with him…</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -7047,8 +7047,8 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>「Hff, hfu... nng, weird feeling... haa, ah... uhnn...
-it feels... good...？」</t>
+          <t>Hff, hfu... nng, weird feeling... haa, ah... uhnn...
+it feels... good...？</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7263,9 +7263,9 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t>But rather than wanting her to awaken to sexual
-stimulation, it seems she was just out of breath and
-ended up echoing back the words.</t>
+          <t>But rather than wanting them to awaken to sexual
+stimulation, it seems they were just out of breath
+and ended up echoing back the words.</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>But... maybe I should tease her a little.</t>
+          <t>But... maybe I should tease them a little.</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7618,8 +7618,8 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>「U—fu...e？ Wha...t？ Th…is...thiiis...
-uhn...fah...ahh...」</t>
+          <t>U—fu...e？ Wha...t？ Th…is...thiiis...
+uhn...fah...ahh...</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7649,8 +7649,8 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>She looks up at me in a troubled way, tears welling
-in her eyes.</t>
+          <t>They look up at me in a troubled way, tears welling
+in their eyes.</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>「Uhn... ahh... did I... do it, maybe？」</t>
+          <t>Uhn... ahh... did I... do it, maybe？</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t>「Nn, ah... O-Onii-chan...！」</t>
+          <t>Nn, ah... O-Onii-chan...！</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>「Th-that's not what I meant！ N-noooo！！」</t>
+          <t>Th-that's not what I meant！ N-noooo！！</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>It felt good while I was making her feel good, but
+          <t>It felt good while I was making them feel good, but
 maybe I really did overdo it…….</t>
         </is>
       </c>
@@ -9411,8 +9411,8 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>「Shall we warm up in the tub a bit before getting
-out...？」</t>
+          <t>Shall we warm up in the tub a bit before getting
+out...？</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>「U-uhn…………！」</t>
+          <t>U-uhn…………！</t>
         </is>
       </c>
       <c r="C585" t="n">
